--- a/RETUNE_recruitment.xlsx
+++ b/RETUNE_recruitment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usbch.sharepoint.com/teams/c0620/Freigegebene Dokumente/RETUNE/18_website/RETUNE_website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1622" documentId="8_{51399C67-AD59-964E-9247-4C3D428189F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8506601-19C5-E548-9AE6-CE95BF655343}"/>
+  <xr:revisionPtr revIDLastSave="1703" documentId="8_{51399C67-AD59-964E-9247-4C3D428189F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3812A31D-370D-1845-93E1-408D6F4C13F7}"/>
   <bookViews>
-    <workbookView xWindow="23360" yWindow="3480" windowWidth="25820" windowHeight="17100" xr2:uid="{1D389274-2DC7-8A41-9A7B-CCBF56013A3F}"/>
+    <workbookView xWindow="6620" yWindow="720" windowWidth="41100" windowHeight="25420" xr2:uid="{1D389274-2DC7-8A41-9A7B-CCBF56013A3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="14">
   <si>
     <t>Date</t>
   </si>
@@ -490,7 +490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDFC9B8A-85DD-B049-AB11-35BA14E37F74}">
-  <dimension ref="A1:G650"/>
+  <dimension ref="A1:G700"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -7994,7 +7994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="641" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A641" s="10">
         <v>46125</v>
       </c>
@@ -8002,7 +8002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="642" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A642" s="10">
         <v>46126</v>
       </c>
@@ -8010,7 +8010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="643" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A643" s="10">
         <v>46128</v>
       </c>
@@ -8018,7 +8018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="644" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A644" s="10">
         <v>46129</v>
       </c>
@@ -8026,7 +8026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="645" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A645" s="10">
         <v>46132</v>
       </c>
@@ -8034,7 +8034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="646" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A646" s="10">
         <v>46133</v>
       </c>
@@ -8042,7 +8042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="647" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A647" s="10">
         <v>46135</v>
       </c>
@@ -8050,7 +8050,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="648" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A648" s="10">
         <v>46136</v>
       </c>
@@ -8058,7 +8058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="649" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A649" s="10">
         <v>46140</v>
       </c>
@@ -8066,11 +8066,611 @@
         <v>1</v>
       </c>
     </row>
-    <row r="650" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A650" s="10">
         <v>46141</v>
       </c>
       <c r="E650">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="651" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A651" s="7">
+        <v>46169</v>
+      </c>
+      <c r="B651" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C651">
+        <v>1</v>
+      </c>
+      <c r="D651" s="8">
+        <v>0</v>
+      </c>
+      <c r="E651" s="8"/>
+      <c r="F651" s="8"/>
+    </row>
+    <row r="652" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A652" s="7">
+        <v>46169</v>
+      </c>
+      <c r="B652" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C652">
+        <v>1</v>
+      </c>
+      <c r="D652" s="8">
+        <v>0</v>
+      </c>
+      <c r="E652" s="8"/>
+      <c r="F652" s="8"/>
+    </row>
+    <row r="653" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A653" s="7">
+        <v>46169</v>
+      </c>
+      <c r="B653" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C653">
+        <v>1</v>
+      </c>
+      <c r="D653" s="8">
+        <v>0</v>
+      </c>
+      <c r="E653" s="8"/>
+      <c r="F653" s="8"/>
+    </row>
+    <row r="654" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A654" s="7">
+        <v>46169</v>
+      </c>
+      <c r="B654" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C654">
+        <v>1</v>
+      </c>
+      <c r="D654" s="8">
+        <v>0</v>
+      </c>
+      <c r="E654" s="8"/>
+      <c r="F654" s="8"/>
+    </row>
+    <row r="655" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A655" s="7">
+        <v>46164</v>
+      </c>
+      <c r="B655" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C655">
+        <v>1</v>
+      </c>
+      <c r="D655" s="8">
+        <v>1</v>
+      </c>
+      <c r="E655" s="8"/>
+      <c r="F655" s="8"/>
+    </row>
+    <row r="656" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A656" s="7">
+        <v>46163</v>
+      </c>
+      <c r="B656" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C656">
+        <v>1</v>
+      </c>
+      <c r="D656" s="8">
+        <v>0</v>
+      </c>
+      <c r="E656" s="8"/>
+      <c r="F656" s="8"/>
+    </row>
+    <row r="657" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A657" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B657" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C657">
+        <v>1</v>
+      </c>
+      <c r="D657" s="8">
+        <v>1</v>
+      </c>
+      <c r="E657" s="8"/>
+      <c r="F657" s="8"/>
+    </row>
+    <row r="658" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A658" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B658" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C658">
+        <v>1</v>
+      </c>
+      <c r="D658" s="8">
+        <v>1</v>
+      </c>
+      <c r="E658" s="8"/>
+      <c r="F658" s="8"/>
+    </row>
+    <row r="659" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A659" s="7">
+        <v>46160</v>
+      </c>
+      <c r="B659" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C659">
+        <v>1</v>
+      </c>
+      <c r="D659" s="8">
+        <v>1</v>
+      </c>
+      <c r="E659" s="8"/>
+      <c r="F659" s="8"/>
+    </row>
+    <row r="660" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A660" s="7">
+        <v>46155</v>
+      </c>
+      <c r="B660" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C660">
+        <v>1</v>
+      </c>
+      <c r="D660" s="8">
+        <v>0</v>
+      </c>
+      <c r="E660" s="8"/>
+      <c r="F660" s="8"/>
+    </row>
+    <row r="661" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A661" s="7">
+        <v>46155</v>
+      </c>
+      <c r="B661" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C661">
+        <v>1</v>
+      </c>
+      <c r="D661" s="8">
+        <v>0</v>
+      </c>
+      <c r="E661" s="8"/>
+      <c r="F661" s="8"/>
+    </row>
+    <row r="662" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A662" s="7">
+        <v>46154</v>
+      </c>
+      <c r="B662" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C662">
+        <v>1</v>
+      </c>
+      <c r="D662" s="8">
+        <v>0</v>
+      </c>
+      <c r="E662" s="8"/>
+      <c r="F662" s="8"/>
+    </row>
+    <row r="663" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A663" s="7">
+        <v>46153</v>
+      </c>
+      <c r="B663" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C663">
+        <v>1</v>
+      </c>
+      <c r="D663" s="8">
+        <v>0</v>
+      </c>
+      <c r="E663" s="8"/>
+      <c r="F663" s="8"/>
+    </row>
+    <row r="664" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A664" s="7">
+        <v>46150</v>
+      </c>
+      <c r="B664" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C664">
+        <v>1</v>
+      </c>
+      <c r="D664" s="8">
+        <v>1</v>
+      </c>
+      <c r="E664" s="8"/>
+      <c r="F664" s="8"/>
+    </row>
+    <row r="665" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A665" s="7">
+        <v>46148</v>
+      </c>
+      <c r="B665" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C665">
+        <v>1</v>
+      </c>
+      <c r="D665" s="8">
+        <v>0</v>
+      </c>
+      <c r="E665" s="8"/>
+      <c r="F665" s="8"/>
+    </row>
+    <row r="666" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A666" s="7">
+        <v>46147</v>
+      </c>
+      <c r="B666" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C666">
+        <v>1</v>
+      </c>
+      <c r="D666" s="8">
+        <v>0</v>
+      </c>
+      <c r="E666" s="8"/>
+      <c r="F666" s="8"/>
+    </row>
+    <row r="667" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A667" s="7">
+        <v>46133</v>
+      </c>
+      <c r="B667" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C667">
+        <v>1</v>
+      </c>
+      <c r="D667" s="8">
+        <v>0</v>
+      </c>
+      <c r="E667" s="8"/>
+      <c r="F667" s="8"/>
+    </row>
+    <row r="668" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A668" s="7">
+        <v>46121</v>
+      </c>
+      <c r="B668" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C668">
+        <v>1</v>
+      </c>
+      <c r="D668" s="8">
+        <v>0</v>
+      </c>
+      <c r="E668" s="8"/>
+      <c r="F668" s="8"/>
+    </row>
+    <row r="669" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A669" s="7">
+        <v>46100</v>
+      </c>
+      <c r="B669" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C669">
+        <v>1</v>
+      </c>
+      <c r="D669" s="8">
+        <v>0</v>
+      </c>
+      <c r="E669" s="8"/>
+      <c r="F669" s="8"/>
+    </row>
+    <row r="670" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A670" s="7">
+        <v>45834</v>
+      </c>
+      <c r="B670" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C670">
+        <v>1</v>
+      </c>
+      <c r="D670" s="8">
+        <v>0</v>
+      </c>
+      <c r="E670" s="8"/>
+      <c r="F670" s="8"/>
+    </row>
+    <row r="671" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A671" s="7">
+        <v>45919</v>
+      </c>
+      <c r="B671" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C671">
+        <v>1</v>
+      </c>
+      <c r="D671" s="8">
+        <v>0</v>
+      </c>
+      <c r="E671" s="8"/>
+      <c r="F671" s="8"/>
+    </row>
+    <row r="672" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A672" s="7">
+        <v>46143</v>
+      </c>
+      <c r="B672" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C672">
+        <v>1</v>
+      </c>
+      <c r="D672" s="8">
+        <v>1</v>
+      </c>
+      <c r="E672" s="8"/>
+      <c r="F672" s="8"/>
+    </row>
+    <row r="673" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A673" s="7">
+        <v>45804</v>
+      </c>
+      <c r="B673" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C673">
+        <v>1</v>
+      </c>
+      <c r="D673" s="8">
+        <v>0</v>
+      </c>
+      <c r="E673" s="8"/>
+      <c r="F673" s="8"/>
+    </row>
+    <row r="674" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A674" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B674" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C674">
+        <v>1</v>
+      </c>
+      <c r="D674" s="8">
+        <v>0</v>
+      </c>
+      <c r="E674" s="8"/>
+      <c r="F674" s="8"/>
+    </row>
+    <row r="675" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A675" s="7">
+        <v>45799</v>
+      </c>
+      <c r="B675" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C675">
+        <v>1</v>
+      </c>
+      <c r="D675" s="8">
+        <v>0</v>
+      </c>
+      <c r="E675" s="8"/>
+      <c r="F675" s="8"/>
+    </row>
+    <row r="676" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A676" s="10">
+        <v>46141</v>
+      </c>
+      <c r="E676">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="677" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A677" s="10">
+        <v>46142</v>
+      </c>
+      <c r="E677">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="678" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A678" s="10">
+        <v>46143</v>
+      </c>
+      <c r="E678">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="679" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A679" s="10">
+        <v>46146</v>
+      </c>
+      <c r="E679">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="680" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A680" s="10">
+        <v>46147</v>
+      </c>
+      <c r="E680">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="681" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A681" s="10">
+        <v>46148</v>
+      </c>
+      <c r="E681">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="682" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A682" s="10">
+        <v>46149</v>
+      </c>
+      <c r="E682">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="683" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A683" s="10">
+        <v>46150</v>
+      </c>
+      <c r="E683">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="684" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A684" s="10">
+        <v>46153</v>
+      </c>
+      <c r="E684">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="685" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A685" s="10">
+        <v>46154</v>
+      </c>
+      <c r="E685">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="686" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A686" s="10">
+        <v>46155</v>
+      </c>
+      <c r="E686">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="687" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A687" s="10">
+        <v>46156</v>
+      </c>
+      <c r="E687">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="688" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A688" s="10">
+        <v>46157</v>
+      </c>
+      <c r="E688">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="689" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A689" s="10">
+        <v>46160</v>
+      </c>
+      <c r="E689">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="690" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A690" s="10">
+        <v>46161</v>
+      </c>
+      <c r="E690">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="691" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A691" s="10">
+        <v>46162</v>
+      </c>
+      <c r="E691">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="692" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A692" s="10">
+        <v>46163</v>
+      </c>
+      <c r="E692">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="693" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A693" s="10">
+        <v>46164</v>
+      </c>
+      <c r="E693">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="694" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A694" s="10">
+        <v>46167</v>
+      </c>
+      <c r="E694">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="695" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A695" s="10">
+        <v>46168</v>
+      </c>
+      <c r="E695">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="696" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A696" s="10">
+        <v>46169</v>
+      </c>
+      <c r="E696">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="697" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A697" s="10">
+        <v>46170</v>
+      </c>
+      <c r="E697">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="698" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A698" s="10">
+        <v>46148</v>
+      </c>
+      <c r="E698">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="699" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A699" s="10">
+        <v>46154</v>
+      </c>
+      <c r="E699">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="700" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A700" s="10">
+        <v>46163</v>
+      </c>
+      <c r="E700">
         <v>1</v>
       </c>
     </row>
@@ -8324,16 +8924,16 @@
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF03F65C-5CED-4A89-8A63-D9B2AEB56D23}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="4c57b41f-cbf4-457f-bf80-bd53c8e26310"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="ee2de805-d424-449f-84ad-9da0e2dd7d39"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="4c57b41f-cbf4-457f-bf80-bd53c8e26310"/>
-    <ds:schemaRef ds:uri="ee2de805-d424-449f-84ad-9da0e2dd7d39"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/RETUNE_recruitment.xlsx
+++ b/RETUNE_recruitment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usbch.sharepoint.com/teams/c0620/Freigegebene Dokumente/RETUNE/18_website/RETUNE_website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1703" documentId="8_{51399C67-AD59-964E-9247-4C3D428189F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3812A31D-370D-1845-93E1-408D6F4C13F7}"/>
+  <xr:revisionPtr revIDLastSave="1738" documentId="8_{51399C67-AD59-964E-9247-4C3D428189F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24A6116F-34C8-9C47-843C-D336776C3EE4}"/>
   <bookViews>
-    <workbookView xWindow="6620" yWindow="720" windowWidth="41100" windowHeight="25420" xr2:uid="{1D389274-2DC7-8A41-9A7B-CCBF56013A3F}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="18960" xr2:uid="{1D389274-2DC7-8A41-9A7B-CCBF56013A3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="14">
   <si>
     <t>Date</t>
   </si>
@@ -490,7 +490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDFC9B8A-85DD-B049-AB11-35BA14E37F74}">
-  <dimension ref="A1:G700"/>
+  <dimension ref="A1:G716"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -8578,7 +8578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="689" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A689" s="10">
         <v>46160</v>
       </c>
@@ -8586,7 +8586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="690" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A690" s="10">
         <v>46161</v>
       </c>
@@ -8594,7 +8594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="691" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A691" s="10">
         <v>46162</v>
       </c>
@@ -8602,7 +8602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="692" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A692" s="10">
         <v>46163</v>
       </c>
@@ -8610,7 +8610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="693" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A693" s="10">
         <v>46164</v>
       </c>
@@ -8618,7 +8618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="694" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A694" s="10">
         <v>46167</v>
       </c>
@@ -8626,7 +8626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="695" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A695" s="10">
         <v>46168</v>
       </c>
@@ -8634,7 +8634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="696" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A696" s="10">
         <v>46169</v>
       </c>
@@ -8642,7 +8642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="697" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A697" s="10">
         <v>46170</v>
       </c>
@@ -8650,7 +8650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="698" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A698" s="10">
         <v>46148</v>
       </c>
@@ -8658,7 +8658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="699" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A699" s="10">
         <v>46154</v>
       </c>
@@ -8666,11 +8666,203 @@
         <v>1</v>
       </c>
     </row>
-    <row r="700" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A700" s="10">
         <v>46163</v>
       </c>
       <c r="E700">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="701" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A701" s="7">
+        <v>46176</v>
+      </c>
+      <c r="B701" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C701">
+        <v>1</v>
+      </c>
+      <c r="D701" s="8">
+        <v>1</v>
+      </c>
+      <c r="E701" s="8"/>
+      <c r="F701" s="8"/>
+    </row>
+    <row r="702" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A702" s="7">
+        <v>46176</v>
+      </c>
+      <c r="B702" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C702">
+        <v>1</v>
+      </c>
+      <c r="D702" s="8">
+        <v>0</v>
+      </c>
+      <c r="E702" s="8"/>
+      <c r="F702" s="8"/>
+    </row>
+    <row r="703" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A703" s="7">
+        <v>46176</v>
+      </c>
+      <c r="B703" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C703">
+        <v>1</v>
+      </c>
+      <c r="D703" s="8">
+        <v>1</v>
+      </c>
+      <c r="E703" s="8"/>
+      <c r="F703" s="8"/>
+    </row>
+    <row r="704" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A704" s="7">
+        <v>46175</v>
+      </c>
+      <c r="B704" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C704">
+        <v>1</v>
+      </c>
+      <c r="D704" s="8">
+        <v>0</v>
+      </c>
+      <c r="E704" s="8"/>
+      <c r="F704" s="8"/>
+    </row>
+    <row r="705" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A705" s="7">
+        <v>46174</v>
+      </c>
+      <c r="B705" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C705">
+        <v>1</v>
+      </c>
+      <c r="D705" s="8">
+        <v>0</v>
+      </c>
+      <c r="E705" s="8"/>
+      <c r="F705" s="8"/>
+    </row>
+    <row r="706" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A706" s="7">
+        <v>46174</v>
+      </c>
+      <c r="B706" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C706">
+        <v>1</v>
+      </c>
+      <c r="D706" s="8">
+        <v>1</v>
+      </c>
+      <c r="E706" s="8"/>
+      <c r="F706" s="8"/>
+    </row>
+    <row r="707" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A707" s="7">
+        <v>46174</v>
+      </c>
+      <c r="B707" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C707">
+        <v>1</v>
+      </c>
+      <c r="D707" s="8">
+        <v>1</v>
+      </c>
+      <c r="E707" s="8"/>
+      <c r="F707" s="8"/>
+    </row>
+    <row r="708" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A708" s="7">
+        <v>46170</v>
+      </c>
+      <c r="B708" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C708">
+        <v>1</v>
+      </c>
+      <c r="D708" s="8">
+        <v>1</v>
+      </c>
+      <c r="E708" s="8"/>
+      <c r="F708" s="8"/>
+    </row>
+    <row r="709" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A709" s="7">
+        <v>46171</v>
+      </c>
+      <c r="E709">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="710" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A710" s="7">
+        <v>46176</v>
+      </c>
+      <c r="E710">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="711" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A711" s="7">
+        <v>46178</v>
+      </c>
+      <c r="E711">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="712" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A712" s="7">
+        <v>46175</v>
+      </c>
+      <c r="E712">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="713" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A713" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E713">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="714" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A714" s="7">
+        <v>46177</v>
+      </c>
+      <c r="E714">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="715" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A715" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E715">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="716" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A716" s="7">
+        <v>46170</v>
+      </c>
+      <c r="E716">
         <v>1</v>
       </c>
     </row>
@@ -8683,6 +8875,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <Confidentiality xmlns="ee2de805-d424-449f-84ad-9da0e2dd7d39">Intern</Confidentiality>
@@ -8693,15 +8894,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8922,26 +9114,26 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF03F65C-5CED-4A89-8A63-D9B2AEB56D23}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0DBF876-E745-42DF-BD17-181B14022097}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="4c57b41f-cbf4-457f-bf80-bd53c8e26310"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="ee2de805-d424-449f-84ad-9da0e2dd7d39"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0DBF876-E745-42DF-BD17-181B14022097}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF03F65C-5CED-4A89-8A63-D9B2AEB56D23}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="4c57b41f-cbf4-457f-bf80-bd53c8e26310"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="ee2de805-d424-449f-84ad-9da0e2dd7d39"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
